--- a/results/MC_Dist=Exp_n=300_LT=0.3_C=0.2_B=100.xlsx
+++ b/results/MC_Dist=Exp_n=300_LT=0.3_C=0.2_B=100.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -120,13 +120,16 @@
     <t xml:space="preserve">Gamma</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5,1</t>
+    <t xml:space="preserve">1,0.8</t>
   </si>
   <si>
     <t xml:space="preserve">x1.mean</t>
   </si>
   <si>
     <t xml:space="preserve">x1.sd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8</t>
   </si>
   <si>
     <t xml:space="preserve">x2.mean</t>
@@ -542,22 +545,22 @@
         <v>7</v>
       </c>
       <c r="B2" t="n">
-        <v>-1.04460188541007</v>
+        <v>-1.01969018380371</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.0446018854100692</v>
+        <v>-0.0196901838037105</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0269565564807182</v>
+        <v>0.0396520585032627</v>
       </c>
       <c r="E2" t="n">
-        <v>0.158806242080793</v>
+        <v>0.199150608367563</v>
       </c>
       <c r="F2" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="G2" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="3">
@@ -565,22 +568,22 @@
         <v>8</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.97181763454932</v>
+        <v>-0.975709127221621</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0281823654506798</v>
+        <v>0.0242908727783794</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0163785309007125</v>
+        <v>0.0186405873094346</v>
       </c>
       <c r="E3" t="n">
-        <v>0.125465940399457</v>
+        <v>0.135029143165987</v>
       </c>
       <c r="F3" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="G3" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="4">
@@ -588,22 +591,22 @@
         <v>9</v>
       </c>
       <c r="B4" t="n">
-        <v>1.50902847062623</v>
+        <v>1.03562874292709</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0090284706262258</v>
+        <v>0.0356287429270863</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0253154883178519</v>
+        <v>0.030888470276011</v>
       </c>
       <c r="E4" t="n">
-        <v>0.159652321225626</v>
+        <v>0.172968914569994</v>
       </c>
       <c r="F4" t="n">
         <v>0.95</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="5">
@@ -611,22 +614,22 @@
         <v>10</v>
       </c>
       <c r="B5" t="n">
-        <v>1.25623077587191</v>
+        <v>0.98079848491262</v>
       </c>
       <c r="C5" t="n">
-        <v>0.256230775871913</v>
+        <v>0.180798484912621</v>
       </c>
       <c r="D5" t="n">
-        <v>0.171439720317087</v>
+        <v>0.143459364973197</v>
       </c>
       <c r="E5" t="n">
-        <v>0.326885377948185</v>
+        <v>0.334499887252926</v>
       </c>
       <c r="F5" t="n">
-        <v>0.87</v>
+        <v>0.93</v>
       </c>
       <c r="G5" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="6">
@@ -634,22 +637,22 @@
         <v>11</v>
       </c>
       <c r="B6" t="n">
-        <v>2.05042570454184</v>
+        <v>1.98447890467929</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0504257045418406</v>
+        <v>-0.0155210953207083</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00752127166960483</v>
+        <v>0.14467802947951</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0709140893742684</v>
+        <v>0.381963461523409</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9</v>
+        <v>0.99</v>
       </c>
       <c r="G6" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
     </row>
   </sheetData>
@@ -780,20 +783,20 @@
         <v>36</v>
       </c>
       <c r="B15" t="s">
-        <v>7</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B16" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B17" t="s">
         <v>7</v>
@@ -812,2325 +815,2325 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-0.905838284789891</v>
+        <v>-0.879871954169267</v>
       </c>
       <c r="B2" t="n">
-        <v>-1.16140499502818</v>
+        <v>-0.977084711500987</v>
       </c>
       <c r="C2" t="n">
-        <v>1.66166856740823</v>
+        <v>0.978675253160537</v>
       </c>
       <c r="D2" t="n">
-        <v>1.00672313420284</v>
+        <v>0.811751183868697</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.08713183761322</v>
+        <v>-1.44906935409703</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.56865962672863</v>
+        <v>-2.47189177995595</v>
       </c>
       <c r="G2" t="n">
-        <v>2.01049881466289</v>
+        <v>1.97299519912061</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-0.981702631950278</v>
+        <v>-0.852944373543853</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.802745472193731</v>
+        <v>-1.04839901053758</v>
       </c>
       <c r="C3" t="n">
-        <v>1.33366372143398</v>
+        <v>1.13763470431266</v>
       </c>
       <c r="D3" t="n">
-        <v>1.27717545982962</v>
+        <v>0.741724264358821</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.942078018650368</v>
+        <v>-1.27064220668891</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.65530138526356</v>
+        <v>-1.50158563184477</v>
       </c>
       <c r="G3" t="n">
-        <v>2.0153308013874</v>
+        <v>2.02122984532827</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>-0.811349164162316</v>
+        <v>-1.06182902196613</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.856433219819731</v>
+        <v>-1.03821329639948</v>
       </c>
       <c r="C4" t="n">
-        <v>1.45855379706959</v>
+        <v>1.07781322372253</v>
       </c>
       <c r="D4" t="n">
-        <v>0.856892424344919</v>
+        <v>0.9803786586103</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.12696309276611</v>
+        <v>-1.08083430887037</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.60175937939452</v>
+        <v>-2.05139690096511</v>
       </c>
       <c r="G4" t="n">
-        <v>2.01783523568312</v>
+        <v>1.95449269362258</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-1.02230945940114</v>
+        <v>-1.02822954932543</v>
       </c>
       <c r="B5" t="n">
-        <v>-1.03143420923824</v>
+        <v>-0.919186485139438</v>
       </c>
       <c r="C5" t="n">
-        <v>1.49469969009807</v>
+        <v>0.925305233783192</v>
       </c>
       <c r="D5" t="n">
-        <v>1.21980328085509</v>
+        <v>1.36644831321663</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.05533948169658</v>
+        <v>-1.27478016069261</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.43929643688833</v>
+        <v>-1.51602861993</v>
       </c>
       <c r="G5" t="n">
-        <v>1.95480808713875</v>
+        <v>2.04389699998108</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-1.34454956987471</v>
+        <v>-1.19690224243761</v>
       </c>
       <c r="B6" t="n">
-        <v>-1.17596440212066</v>
+        <v>-0.875676174575525</v>
       </c>
       <c r="C6" t="n">
-        <v>1.7867624856468</v>
+        <v>0.804087501685161</v>
       </c>
       <c r="D6" t="n">
-        <v>1.89404336766902</v>
+        <v>1.10803389095911</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.310943827846874</v>
+        <v>-0.584331422133057</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.15092783220985</v>
+        <v>-1.12074951972409</v>
       </c>
       <c r="G6" t="n">
-        <v>2.07184643290198</v>
+        <v>1.9989207769428</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>-0.882840215676764</v>
+        <v>-0.854163902236088</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.789074651412062</v>
+        <v>-0.918732165185627</v>
       </c>
       <c r="C7" t="n">
-        <v>1.28563725175203</v>
+        <v>0.960915249800148</v>
       </c>
       <c r="D7" t="n">
-        <v>0.98012718247334</v>
+        <v>0.600033918388425</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.33508310996981</v>
+        <v>-1.1359265317166</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.7099450757927</v>
+        <v>-1.45585595583725</v>
       </c>
       <c r="G7" t="n">
-        <v>2.07565549886139</v>
+        <v>1.97428438483351</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>-1.19436769527974</v>
+        <v>-0.909176561986903</v>
       </c>
       <c r="B8" t="n">
-        <v>-1.17695129008539</v>
+        <v>-0.926064346590495</v>
       </c>
       <c r="C8" t="n">
-        <v>1.73842524830401</v>
+        <v>1.19939907339565</v>
       </c>
       <c r="D8" t="n">
-        <v>1.31361460810921</v>
+        <v>0.896964802760714</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.759847414346219</v>
+        <v>-1.28959490516094</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.60391263682731</v>
+        <v>-2.36315554297858</v>
       </c>
       <c r="G8" t="n">
-        <v>2.09419361390886</v>
+        <v>2.13858774916544</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>-1.28231677871808</v>
+        <v>-1.2219057504803</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.876838120230731</v>
+        <v>-0.87173021516069</v>
       </c>
       <c r="C9" t="n">
-        <v>1.30796952155954</v>
+        <v>1.02320599236493</v>
       </c>
       <c r="D9" t="n">
-        <v>1.78648887421883</v>
+        <v>1.38165545523737</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.633065019324055</v>
+        <v>-0.930602211554477</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.27418851598749</v>
+        <v>-1.92016615975689</v>
       </c>
       <c r="G9" t="n">
-        <v>2.01273011483496</v>
+        <v>2.16595273641496</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>-0.864522004671469</v>
+        <v>-0.899906206195123</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.963840371376818</v>
+        <v>-1.17664589811221</v>
       </c>
       <c r="C10" t="n">
-        <v>1.52586452920015</v>
+        <v>1.2095483681588</v>
       </c>
       <c r="D10" t="n">
-        <v>0.811481130789916</v>
+        <v>1.00641935560065</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.27768088651844</v>
+        <v>-1.31769250547277</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.66856391243425</v>
+        <v>-1.63434900019793</v>
       </c>
       <c r="G10" t="n">
-        <v>1.98649051074399</v>
+        <v>2.0574417454806</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-1.17685155233022</v>
+        <v>-1.04307642697449</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.965481734911591</v>
+        <v>-1.12229873629035</v>
       </c>
       <c r="C11" t="n">
-        <v>1.49687321414267</v>
+        <v>1.00746012770285</v>
       </c>
       <c r="D11" t="n">
-        <v>1.54132687991175</v>
+        <v>1.21566332292487</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.979930388148473</v>
+        <v>-1.09501014415693</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.98374169752003</v>
+        <v>-1.52605687437905</v>
       </c>
       <c r="G11" t="n">
-        <v>2.0382569173067</v>
+        <v>1.95250168007236</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>-0.988799281052091</v>
+        <v>-1.01250379391803</v>
       </c>
       <c r="B12" t="n">
-        <v>-1.17846871756967</v>
+        <v>-1.10995242310603</v>
       </c>
       <c r="C12" t="n">
-        <v>1.75857291309854</v>
+        <v>1.3451943470836</v>
       </c>
       <c r="D12" t="n">
-        <v>0.871581458486459</v>
+        <v>0.974577526404131</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.823439756803771</v>
+        <v>-1.42248522660122</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.17155494158526</v>
+        <v>-1.46630762658939</v>
       </c>
       <c r="G12" t="n">
-        <v>2.15775010889632</v>
+        <v>2.03187742470682</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>-1.10913600653487</v>
+        <v>-0.931029838595309</v>
       </c>
       <c r="B13" t="n">
-        <v>-1.12554144792979</v>
+        <v>-0.70762470723919</v>
       </c>
       <c r="C13" t="n">
-        <v>1.71145312245852</v>
+        <v>0.726480307663635</v>
       </c>
       <c r="D13" t="n">
-        <v>1.28034303952382</v>
+        <v>0.980339883795258</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.830571544809334</v>
+        <v>-1.07338985012129</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.39740664362485</v>
+        <v>-1.62551317063032</v>
       </c>
       <c r="G13" t="n">
-        <v>1.96468980807748</v>
+        <v>2.06393765643428</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>-1.11469360281906</v>
+        <v>-1.01915799338848</v>
       </c>
       <c r="B14" t="n">
-        <v>-1.0089752334628</v>
+        <v>-0.922659808033773</v>
       </c>
       <c r="C14" t="n">
-        <v>1.42833304635829</v>
+        <v>0.908514147375347</v>
       </c>
       <c r="D14" t="n">
-        <v>1.38186603020287</v>
+        <v>1.24463376478989</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.976566011470019</v>
+        <v>-1.32676171575238</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.44844660236316</v>
+        <v>-1.47141287983698</v>
       </c>
       <c r="G14" t="n">
-        <v>2.04567153655158</v>
+        <v>2.12517889226535</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>-0.809513157572479</v>
+        <v>-1.06005480694154</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.988285383109629</v>
+        <v>-1.09510196874737</v>
       </c>
       <c r="C15" t="n">
-        <v>1.52859513937134</v>
+        <v>1.13271212170864</v>
       </c>
       <c r="D15" t="n">
-        <v>0.894399222816457</v>
+        <v>1.14469788965228</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.10128655694772</v>
+        <v>-0.887826729998646</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.64286328182921</v>
+        <v>-1.42665049342001</v>
       </c>
       <c r="G15" t="n">
-        <v>1.99514166237119</v>
+        <v>2.1474554283993</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>-1.32676396664731</v>
+        <v>-0.979434780524294</v>
       </c>
       <c r="B16" t="n">
-        <v>-1.07442231019342</v>
+        <v>-0.953740289537014</v>
       </c>
       <c r="C16" t="n">
-        <v>1.45390137679566</v>
+        <v>1.09608360584462</v>
       </c>
       <c r="D16" t="n">
-        <v>1.89319105757201</v>
+        <v>0.846749993889724</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.975136309738053</v>
+        <v>-1.07653124974628</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.22033240286316</v>
+        <v>-2.10291633557808</v>
       </c>
       <c r="G16" t="n">
-        <v>1.98030648884868</v>
+        <v>2.12578388786616</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>-1.01815321159821</v>
+        <v>-1.12674615604565</v>
       </c>
       <c r="B17" t="n">
-        <v>-1.03510952498464</v>
+        <v>-0.950765473863538</v>
       </c>
       <c r="C17" t="n">
-        <v>1.55671335971725</v>
+        <v>1.0464926207575</v>
       </c>
       <c r="D17" t="n">
-        <v>0.876930461648864</v>
+        <v>1.1016073538741</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.913085458482695</v>
+        <v>-1.08708645208425</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.01592333723407</v>
+        <v>-1.27712684572409</v>
       </c>
       <c r="G17" t="n">
-        <v>2.08790099018491</v>
+        <v>1.94358940011032</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>-0.964511010188507</v>
+        <v>-1.11984776813851</v>
       </c>
       <c r="B18" t="n">
-        <v>-0.99547023399457</v>
+        <v>-0.797209060317673</v>
       </c>
       <c r="C18" t="n">
-        <v>1.64989206303785</v>
+        <v>0.984649909777992</v>
       </c>
       <c r="D18" t="n">
-        <v>0.940239015533556</v>
+        <v>1.19696633593872</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.661133135318468</v>
+        <v>-0.705939294356588</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.36700049781183</v>
+        <v>-1.23322455202879</v>
       </c>
       <c r="G18" t="n">
-        <v>2.10702097610212</v>
+        <v>2.03692633401004</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>-1.06635309720043</v>
+        <v>-0.749032242413979</v>
       </c>
       <c r="B19" t="n">
-        <v>-1.01718704343444</v>
+        <v>-0.882521689536255</v>
       </c>
       <c r="C19" t="n">
-        <v>1.53613592722148</v>
+        <v>0.958070974772143</v>
       </c>
       <c r="D19" t="n">
-        <v>1.07242228283899</v>
+        <v>0.495032646563336</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.00295150247058</v>
+        <v>-1.37872210335844</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.06301401695302</v>
+        <v>-1.66249220646879</v>
       </c>
       <c r="G19" t="n">
-        <v>1.93024243276479</v>
+        <v>2.05390835257452</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>-1.16154583015875</v>
+        <v>-1.03876405717217</v>
       </c>
       <c r="B20" t="n">
-        <v>-1.01859696181003</v>
+        <v>-0.858784226552341</v>
       </c>
       <c r="C20" t="n">
-        <v>1.63978201240654</v>
+        <v>0.76933620137637</v>
       </c>
       <c r="D20" t="n">
-        <v>1.66252052233462</v>
+        <v>1.08948983134708</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.887308654096387</v>
+        <v>-0.928060337012998</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.31216609443486</v>
+        <v>-1.38974064668476</v>
       </c>
       <c r="G20" t="n">
-        <v>2.15466407449778</v>
+        <v>2.11453354090269</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>-1.08084925854193</v>
+        <v>-1.09579159633113</v>
       </c>
       <c r="B21" t="n">
-        <v>-0.919741464679382</v>
+        <v>-0.823118770023871</v>
       </c>
       <c r="C21" t="n">
-        <v>1.48517611408544</v>
+        <v>0.902809313852858</v>
       </c>
       <c r="D21" t="n">
-        <v>1.48986368450694</v>
+        <v>1.10659811741057</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.926818347562996</v>
+        <v>-1.15077332619962</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.47872185561127</v>
+        <v>-1.39658461809519</v>
       </c>
       <c r="G21" t="n">
-        <v>2.08095061720024</v>
+        <v>1.99488090100284</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>-1.11387965947488</v>
+        <v>-1.37134201568984</v>
       </c>
       <c r="B22" t="n">
-        <v>-1.0919910342008</v>
+        <v>-1.03129731896789</v>
       </c>
       <c r="C22" t="n">
-        <v>1.63218751631832</v>
+        <v>1.10053551089398</v>
       </c>
       <c r="D22" t="n">
-        <v>1.32032518117804</v>
+        <v>2.03879372858452</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.15759409748826</v>
+        <v>-1.16154961152831</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.36394362312422</v>
+        <v>-1.50135971851021</v>
       </c>
       <c r="G22" t="n">
-        <v>1.95511462622028</v>
+        <v>1.96000479090159</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>-1.10265119787902</v>
+        <v>-1.14519748082808</v>
       </c>
       <c r="B23" t="n">
-        <v>-1.02385548118545</v>
+        <v>-0.977922225102889</v>
       </c>
       <c r="C23" t="n">
-        <v>1.51284808103118</v>
+        <v>1.06513352386806</v>
       </c>
       <c r="D23" t="n">
-        <v>1.4634308283601</v>
+        <v>1.28562790014116</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.777973944265446</v>
+        <v>-1.04968394891015</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.30176456182174</v>
+        <v>-1.43385936646959</v>
       </c>
       <c r="G23" t="n">
-        <v>2.01660590871918</v>
+        <v>1.94921252455157</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>-0.946897413572566</v>
+        <v>-1.18202493315725</v>
       </c>
       <c r="B24" t="n">
-        <v>-1.02968339911905</v>
+        <v>-0.84534909397639</v>
       </c>
       <c r="C24" t="n">
-        <v>1.53110075164374</v>
+        <v>0.78225620726129</v>
       </c>
       <c r="D24" t="n">
-        <v>1.12326983040071</v>
+        <v>1.27987229219291</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.49551142332939</v>
+        <v>-0.708745634926705</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.35560474378152</v>
+        <v>-1.29284976266668</v>
       </c>
       <c r="G24" t="n">
-        <v>1.98715914196283</v>
+        <v>2.04206429337693</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>-1.04594419326092</v>
+        <v>-0.63057627528814</v>
       </c>
       <c r="B25" t="n">
-        <v>-0.949506964077419</v>
+        <v>-0.937968547115952</v>
       </c>
       <c r="C25" t="n">
-        <v>1.38971648770175</v>
+        <v>0.971930172403028</v>
       </c>
       <c r="D25" t="n">
-        <v>0.991748694534328</v>
+        <v>0.437110614870785</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.779145323569819</v>
+        <v>-1.65530136325554</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.34126775057635</v>
+        <v>-2.01239264111574</v>
       </c>
       <c r="G25" t="n">
-        <v>2.06877157544527</v>
+        <v>2.04386712912321</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>-1.16234909050076</v>
+        <v>-1.35404325227193</v>
       </c>
       <c r="B26" t="n">
-        <v>-1.39321257139115</v>
+        <v>-1.3076069424787</v>
       </c>
       <c r="C26" t="n">
-        <v>1.81504191061246</v>
+        <v>1.63674687122659</v>
       </c>
       <c r="D26" t="n">
-        <v>1.35544709470967</v>
+        <v>1.04603423632108</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.803195529697145</v>
+        <v>-0.535837080071794</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.34491579421754</v>
+        <v>-1.35918096415306</v>
       </c>
       <c r="G26" t="n">
-        <v>1.92194961027982</v>
+        <v>2.02610835009121</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>-0.660873442758611</v>
+        <v>-1.25746803008049</v>
       </c>
       <c r="B27" t="n">
-        <v>-0.999204812366872</v>
+        <v>-1.07167735774149</v>
       </c>
       <c r="C27" t="n">
-        <v>1.29598471572129</v>
+        <v>1.16403722552022</v>
       </c>
       <c r="D27" t="n">
-        <v>0.536111440375245</v>
+        <v>1.30211049371912</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.32064668216446</v>
+        <v>-0.834094609367758</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.87745345170287</v>
+        <v>-1.85003928285588</v>
       </c>
       <c r="G27" t="n">
-        <v>1.9408679381416</v>
+        <v>2.06068443255266</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>-1.37923241545488</v>
+        <v>-1.46842745495511</v>
       </c>
       <c r="B28" t="n">
-        <v>-0.772848139139523</v>
+        <v>-1.0315906973905</v>
       </c>
       <c r="C28" t="n">
-        <v>1.33302216752853</v>
+        <v>0.946662894169938</v>
       </c>
       <c r="D28" t="n">
-        <v>1.8774152721773</v>
+        <v>1.70267841355799</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.457026732672729</v>
+        <v>-0.581775523555721</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.15105499108966</v>
+        <v>-0.919036239309809</v>
       </c>
       <c r="G28" t="n">
-        <v>2.05767737069881</v>
+        <v>1.93764334641433</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>-1.08158675433332</v>
+        <v>-0.948663714675911</v>
       </c>
       <c r="B29" t="n">
-        <v>-0.93940066914072</v>
+        <v>-0.955505489298699</v>
       </c>
       <c r="C29" t="n">
-        <v>1.67732363625836</v>
+        <v>0.971889760243365</v>
       </c>
       <c r="D29" t="n">
-        <v>1.45831125876919</v>
+        <v>0.912362344039272</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.811992764047932</v>
+        <v>-0.909568316147091</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.37842776468135</v>
+        <v>-1.56321576224418</v>
       </c>
       <c r="G29" t="n">
-        <v>2.24128777113746</v>
+        <v>1.98482944513817</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>-1.3029059569464</v>
+        <v>-0.771597343531599</v>
       </c>
       <c r="B30" t="n">
-        <v>-0.920287407301736</v>
+        <v>-0.913659759588689</v>
       </c>
       <c r="C30" t="n">
-        <v>1.37401841281615</v>
+        <v>1.04895692828437</v>
       </c>
       <c r="D30" t="n">
-        <v>1.69609500900379</v>
+        <v>0.529229254723839</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.437595298096025</v>
+        <v>-1.23246447108766</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.10058392880635</v>
+        <v>-1.73847502238939</v>
       </c>
       <c r="G30" t="n">
-        <v>2.06715196097274</v>
+        <v>2.00627469077294</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>-0.69641671869766</v>
+        <v>-1.23309292836997</v>
       </c>
       <c r="B31" t="n">
-        <v>-1.03296846421892</v>
+        <v>-1.02211769507316</v>
       </c>
       <c r="C31" t="n">
-        <v>1.39545086231394</v>
+        <v>0.993928999440249</v>
       </c>
       <c r="D31" t="n">
-        <v>0.589672367412189</v>
+        <v>1.30265371785905</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.45837440959319</v>
+        <v>-0.912906446340429</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.92902126439682</v>
+        <v>-1.16315224482019</v>
       </c>
       <c r="G31" t="n">
-        <v>1.97033711525981</v>
+        <v>1.97892821643159</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>-1.12954832066189</v>
+        <v>-1.18700923906503</v>
       </c>
       <c r="B32" t="n">
-        <v>-0.982481952924371</v>
+        <v>-1.04602379776175</v>
       </c>
       <c r="C32" t="n">
-        <v>1.67152418253207</v>
+        <v>1.01978546682407</v>
       </c>
       <c r="D32" t="n">
-        <v>1.33736327989763</v>
+        <v>1.04134405586036</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.915363082946104</v>
+        <v>-0.781392950973634</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.29665768913872</v>
+        <v>-1.07412194596082</v>
       </c>
       <c r="G32" t="n">
-        <v>2.10832491337282</v>
+        <v>1.97089210528367</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>-0.67954249674443</v>
+        <v>-0.84884712860443</v>
       </c>
       <c r="B33" t="n">
-        <v>-0.951848747038862</v>
+        <v>-1.05254917067061</v>
       </c>
       <c r="C33" t="n">
-        <v>1.62966126012919</v>
+        <v>1.06707822492385</v>
       </c>
       <c r="D33" t="n">
-        <v>0.556630523719173</v>
+        <v>0.696756435377442</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.5312813189823</v>
+        <v>-1.39247795435888</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.75306659635391</v>
+        <v>-1.62482801808456</v>
       </c>
       <c r="G33" t="n">
-        <v>2.08428438987786</v>
+        <v>1.89967733113012</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>-0.819272768084087</v>
+        <v>-0.790018495429115</v>
       </c>
       <c r="B34" t="n">
-        <v>-0.91929678198419</v>
+        <v>-0.755208077621386</v>
       </c>
       <c r="C34" t="n">
-        <v>1.32546148563644</v>
+        <v>0.8630270499792</v>
       </c>
       <c r="D34" t="n">
-        <v>0.745764806101831</v>
+        <v>0.479404321945823</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.941263718476288</v>
+        <v>-1.27321595781309</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.65363387682231</v>
+        <v>-1.69580989379949</v>
       </c>
       <c r="G34" t="n">
-        <v>1.97038454448575</v>
+        <v>2.12988343406519</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>-0.904942351720019</v>
+        <v>-0.957821316614067</v>
       </c>
       <c r="B35" t="n">
-        <v>-1.0511134088985</v>
+        <v>-1.05882790568576</v>
       </c>
       <c r="C35" t="n">
-        <v>1.61612455402253</v>
+        <v>1.08632122192555</v>
       </c>
       <c r="D35" t="n">
-        <v>1.07488674233345</v>
+        <v>0.703267148671871</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.31971032009455</v>
+        <v>-0.666115640877649</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.56882500970931</v>
+        <v>-1.32340402031591</v>
       </c>
       <c r="G35" t="n">
-        <v>2.0997060774678</v>
+        <v>2.04622643443396</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>-0.974206254142969</v>
+        <v>-1.17427947522298</v>
       </c>
       <c r="B36" t="n">
-        <v>-0.960246520768136</v>
+        <v>-0.880042500819502</v>
       </c>
       <c r="C36" t="n">
-        <v>1.60453251421494</v>
+        <v>1.07134937278502</v>
       </c>
       <c r="D36" t="n">
-        <v>1.28475942989518</v>
+        <v>1.33092499206018</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.26142797667442</v>
+        <v>-1.08184918028302</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.53350727125806</v>
+        <v>-1.28641138711845</v>
       </c>
       <c r="G36" t="n">
-        <v>2.14517870160893</v>
+        <v>1.99024086966797</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>-0.882012265371138</v>
+        <v>-0.89630507168223</v>
       </c>
       <c r="B37" t="n">
-        <v>-0.982717441069505</v>
+        <v>-1.07925377828229</v>
       </c>
       <c r="C37" t="n">
-        <v>1.3788683806509</v>
+        <v>1.17839504156995</v>
       </c>
       <c r="D37" t="n">
-        <v>0.743715307561192</v>
+        <v>0.757779177113537</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.20749834381581</v>
+        <v>-0.990215603092452</v>
       </c>
       <c r="F37" t="n">
-        <v>-2.18633069467845</v>
+        <v>-1.62198864449002</v>
       </c>
       <c r="G37" t="n">
-        <v>2.04678097984215</v>
+        <v>1.96961019493047</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>-1.04568246228533</v>
+        <v>-0.979311870349741</v>
       </c>
       <c r="B38" t="n">
-        <v>-0.91843038412241</v>
+        <v>-1.18041169041014</v>
       </c>
       <c r="C38" t="n">
-        <v>1.24099869788217</v>
+        <v>1.20350709656704</v>
       </c>
       <c r="D38" t="n">
-        <v>1.12868885868382</v>
+        <v>0.855595553181231</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.698820567554205</v>
+        <v>-1.06646765006495</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.40394250096051</v>
+        <v>-2.18766788511733</v>
       </c>
       <c r="G38" t="n">
-        <v>2.1300106442066</v>
+        <v>2.01519769738636</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>-1.12740431277153</v>
+        <v>-1.12076490660213</v>
       </c>
       <c r="B39" t="n">
-        <v>-0.917662490307174</v>
+        <v>-1.06531247453253</v>
       </c>
       <c r="C39" t="n">
-        <v>1.55652172782953</v>
+        <v>0.957014134500419</v>
       </c>
       <c r="D39" t="n">
-        <v>1.63902424921023</v>
+        <v>1.00015604056787</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.15001863027553</v>
+        <v>-1.0402303319865</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.38956791231834</v>
+        <v>-1.85633255798848</v>
       </c>
       <c r="G39" t="n">
-        <v>2.0754417168548</v>
+        <v>1.95407877575959</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>-1.02050832038056</v>
+        <v>-0.780019783061046</v>
       </c>
       <c r="B40" t="n">
-        <v>-0.819472129141103</v>
+        <v>-0.854447105487124</v>
       </c>
       <c r="C40" t="n">
-        <v>1.37466814135174</v>
+        <v>0.894328700806428</v>
       </c>
       <c r="D40" t="n">
-        <v>1.0879767966621</v>
+        <v>0.657592196454788</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.779903643002113</v>
+        <v>-1.30298826165862</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.37589808384866</v>
+        <v>-1.7073433477076</v>
       </c>
       <c r="G40" t="n">
-        <v>2.04849548382393</v>
+        <v>2.16324068754635</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>-1.06268551712253</v>
+        <v>-1.18980012547509</v>
       </c>
       <c r="B41" t="n">
-        <v>-0.87404572200965</v>
+        <v>-0.823801213682084</v>
       </c>
       <c r="C41" t="n">
-        <v>1.2794812982371</v>
+        <v>0.839626217363726</v>
       </c>
       <c r="D41" t="n">
-        <v>1.38118704499678</v>
+        <v>1.32843552916213</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.895395764987239</v>
+        <v>-1.03800638135778</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.40764561120732</v>
+        <v>-1.2773444222115</v>
       </c>
       <c r="G41" t="n">
-        <v>2.02728007944876</v>
+        <v>1.98004212673141</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>-0.959661612784816</v>
+        <v>-0.63970305358877</v>
       </c>
       <c r="B42" t="n">
-        <v>-1.07588736929826</v>
+        <v>-1.18960115211915</v>
       </c>
       <c r="C42" t="n">
-        <v>1.56215112407789</v>
+        <v>1.13996730697183</v>
       </c>
       <c r="D42" t="n">
-        <v>1.29982746195179</v>
+        <v>0.441070721986158</v>
       </c>
       <c r="E42" t="n">
-        <v>-1.24091848194808</v>
+        <v>-1.38428314845171</v>
       </c>
       <c r="F42" t="n">
-        <v>-1.65997168672035</v>
+        <v>-1.7127369180224</v>
       </c>
       <c r="G42" t="n">
-        <v>2.05070831105314</v>
+        <v>1.94943789085741</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>-0.780315538155135</v>
+        <v>-0.818621033212051</v>
       </c>
       <c r="B43" t="n">
-        <v>-1.02737436203876</v>
+        <v>-1.06766889540178</v>
       </c>
       <c r="C43" t="n">
-        <v>1.50261639001668</v>
+        <v>1.12208670301766</v>
       </c>
       <c r="D43" t="n">
-        <v>0.834516303877405</v>
+        <v>0.494715814698535</v>
       </c>
       <c r="E43" t="n">
-        <v>-1.35475780556867</v>
+        <v>-1.00685204674747</v>
       </c>
       <c r="F43" t="n">
-        <v>-1.82010065369907</v>
+        <v>-1.52359308639089</v>
       </c>
       <c r="G43" t="n">
-        <v>2.078429900738</v>
+        <v>1.96355656624536</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>-1.17342014257309</v>
+        <v>-0.952283755516088</v>
       </c>
       <c r="B44" t="n">
-        <v>-0.95396613652414</v>
+        <v>-0.962290435170006</v>
       </c>
       <c r="C44" t="n">
-        <v>1.39873117049509</v>
+        <v>1.11671103476199</v>
       </c>
       <c r="D44" t="n">
-        <v>1.40047815300108</v>
+        <v>0.621185080817815</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.62786429947588</v>
+        <v>-0.849897373023003</v>
       </c>
       <c r="F44" t="n">
-        <v>-1.12491355043679</v>
+        <v>-1.4753290475276</v>
       </c>
       <c r="G44" t="n">
-        <v>2.16063835262604</v>
+        <v>1.99906620693836</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>-1.24997953587474</v>
+        <v>-0.960816579784937</v>
       </c>
       <c r="B45" t="n">
-        <v>-1.11804721552777</v>
+        <v>-0.946818485755908</v>
       </c>
       <c r="C45" t="n">
-        <v>1.60021106977555</v>
+        <v>1.08619553723751</v>
       </c>
       <c r="D45" t="n">
-        <v>1.67502508064607</v>
+        <v>0.897140708528202</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.715729118277476</v>
+        <v>-1.03234569118256</v>
       </c>
       <c r="F45" t="n">
-        <v>-1.25883164384959</v>
+        <v>-1.54333609912547</v>
       </c>
       <c r="G45" t="n">
-        <v>2.00517141107258</v>
+        <v>1.99559939993334</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>-1.05077735905328</v>
+        <v>-0.679269252121684</v>
       </c>
       <c r="B46" t="n">
-        <v>-0.776378932645174</v>
+        <v>-0.709266455734031</v>
       </c>
       <c r="C46" t="n">
-        <v>1.30713846618322</v>
+        <v>0.669016313616698</v>
       </c>
       <c r="D46" t="n">
-        <v>1.22884135818076</v>
+        <v>0.685929349180318</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.994020723628979</v>
+        <v>-1.51739302501604</v>
       </c>
       <c r="F46" t="n">
-        <v>-1.40967832896325</v>
+        <v>-1.86473469636094</v>
       </c>
       <c r="G46" t="n">
-        <v>2.13162532595412</v>
+        <v>2.04565984709161</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>-1.34258814592576</v>
+        <v>-0.852800051122907</v>
       </c>
       <c r="B47" t="n">
-        <v>-0.742956309167068</v>
+        <v>-0.926803235302336</v>
       </c>
       <c r="C47" t="n">
-        <v>1.58086190471253</v>
+        <v>0.931982271953212</v>
       </c>
       <c r="D47" t="n">
-        <v>2.02536694967247</v>
+        <v>0.784606125002212</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.71954072655626</v>
+        <v>-1.19852527356531</v>
       </c>
       <c r="F47" t="n">
-        <v>-1.21926365391336</v>
+        <v>-1.64270367733438</v>
       </c>
       <c r="G47" t="n">
-        <v>2.13289232647869</v>
+        <v>2.12443577136199</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>-1.09254748740126</v>
+        <v>-1.06403900024402</v>
       </c>
       <c r="B48" t="n">
-        <v>-1.08868052627898</v>
+        <v>-0.903558558501789</v>
       </c>
       <c r="C48" t="n">
-        <v>1.58078399560743</v>
+        <v>1.08617030424014</v>
       </c>
       <c r="D48" t="n">
-        <v>1.39538257986013</v>
+        <v>1.00191797982189</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.840074925044975</v>
+        <v>-1.00145736682966</v>
       </c>
       <c r="F48" t="n">
-        <v>-1.46058404055808</v>
+        <v>-1.19212733605602</v>
       </c>
       <c r="G48" t="n">
-        <v>1.99488078188665</v>
+        <v>2.10204331209282</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>-1.02903460343254</v>
+        <v>-1.02658848918918</v>
       </c>
       <c r="B49" t="n">
-        <v>-1.05531716403687</v>
+        <v>-0.85265586522031</v>
       </c>
       <c r="C49" t="n">
-        <v>1.40740845561098</v>
+        <v>0.854562342787026</v>
       </c>
       <c r="D49" t="n">
-        <v>1.2478527889986</v>
+        <v>0.95507116866272</v>
       </c>
       <c r="E49" t="n">
-        <v>-1.18282797823262</v>
+        <v>-0.863502473976874</v>
       </c>
       <c r="F49" t="n">
-        <v>-1.52596551003082</v>
+        <v>-1.47767594405119</v>
       </c>
       <c r="G49" t="n">
-        <v>2.04525766673766</v>
+        <v>2.00883652093451</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>-1.20182823065968</v>
+        <v>-0.923781572431509</v>
       </c>
       <c r="B50" t="n">
-        <v>-0.988928445463376</v>
+        <v>-0.984659403976971</v>
       </c>
       <c r="C50" t="n">
-        <v>1.75681957627823</v>
+        <v>1.05968166896206</v>
       </c>
       <c r="D50" t="n">
-        <v>1.36442666261037</v>
+        <v>0.914359062908875</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.868413671619713</v>
+        <v>-1.1847312389591</v>
       </c>
       <c r="F50" t="n">
-        <v>-1.13685474721624</v>
+        <v>-1.70194381077985</v>
       </c>
       <c r="G50" t="n">
-        <v>2.15971604975101</v>
+        <v>1.9838186828896</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>-0.828733072753412</v>
+        <v>-0.901261248355833</v>
       </c>
       <c r="B51" t="n">
-        <v>-0.897833299353249</v>
+        <v>-1.05913501666496</v>
       </c>
       <c r="C51" t="n">
-        <v>1.36895156762077</v>
+        <v>1.0460868293684</v>
       </c>
       <c r="D51" t="n">
-        <v>0.910548762368948</v>
+        <v>0.972138355913968</v>
       </c>
       <c r="E51" t="n">
-        <v>-1.30698155114311</v>
+        <v>-1.21775025049821</v>
       </c>
       <c r="F51" t="n">
-        <v>-1.65739264407431</v>
+        <v>-1.75064106405399</v>
       </c>
       <c r="G51" t="n">
-        <v>1.98826703546871</v>
+        <v>1.96365001249059</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>-0.95222528933162</v>
+        <v>-1.03733437984539</v>
       </c>
       <c r="B52" t="n">
-        <v>-0.873653633318981</v>
+        <v>-0.837287437459283</v>
       </c>
       <c r="C52" t="n">
-        <v>1.59341027503123</v>
+        <v>0.892685746332416</v>
       </c>
       <c r="D52" t="n">
-        <v>1.16470966249783</v>
+        <v>1.05566547933705</v>
       </c>
       <c r="E52" t="n">
-        <v>-1.08961694958484</v>
+        <v>-1.05722777508972</v>
       </c>
       <c r="F52" t="n">
-        <v>-1.42081809357511</v>
+        <v>-1.4038249127882</v>
       </c>
       <c r="G52" t="n">
-        <v>2.09618134008298</v>
+        <v>2.11365511426722</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>-0.756259872060678</v>
+        <v>-1.10340372647011</v>
       </c>
       <c r="B53" t="n">
-        <v>-0.791574606431304</v>
+        <v>-0.985062792180614</v>
       </c>
       <c r="C53" t="n">
-        <v>1.40676938062103</v>
+        <v>1.16418598984338</v>
       </c>
       <c r="D53" t="n">
-        <v>0.840466228170655</v>
+        <v>0.935748493360043</v>
       </c>
       <c r="E53" t="n">
-        <v>-1.64743667975607</v>
+        <v>-0.859790349561245</v>
       </c>
       <c r="F53" t="n">
-        <v>-1.86349518346926</v>
+        <v>-1.32171058002024</v>
       </c>
       <c r="G53" t="n">
-        <v>2.06954237217753</v>
+        <v>1.96305860194377</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>-1.14551341747125</v>
+        <v>-1.16023777836023</v>
       </c>
       <c r="B54" t="n">
-        <v>-0.731699562367187</v>
+        <v>-0.824025797912112</v>
       </c>
       <c r="C54" t="n">
-        <v>1.17594719111962</v>
+        <v>0.943204447451018</v>
       </c>
       <c r="D54" t="n">
-        <v>1.55305025564373</v>
+        <v>1.17326601034914</v>
       </c>
       <c r="E54" t="n">
-        <v>-1.13610532287431</v>
+        <v>-0.78961842665431</v>
       </c>
       <c r="F54" t="n">
-        <v>-1.30286982007387</v>
+        <v>-1.32269573919015</v>
       </c>
       <c r="G54" t="n">
-        <v>2.04058062192238</v>
+        <v>2.03476792869086</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>-1.08374001327503</v>
+        <v>-0.879232291806651</v>
       </c>
       <c r="B55" t="n">
-        <v>-0.92036573805692</v>
+        <v>-1.03245599526723</v>
       </c>
       <c r="C55" t="n">
-        <v>1.42579638558636</v>
+        <v>1.09790214285389</v>
       </c>
       <c r="D55" t="n">
-        <v>1.25913289899812</v>
+        <v>0.765376591389529</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.869884300536766</v>
+        <v>-1.25895184316205</v>
       </c>
       <c r="F55" t="n">
-        <v>-1.28055685369898</v>
+        <v>-1.69125665519273</v>
       </c>
       <c r="G55" t="n">
-        <v>2.01559358761922</v>
+        <v>2.0021587376863</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>-0.91566065877094</v>
+        <v>-1.43517914922788</v>
       </c>
       <c r="B56" t="n">
-        <v>-0.748726778789922</v>
+        <v>-1.08914678762381</v>
       </c>
       <c r="C56" t="n">
-        <v>1.23169348548403</v>
+        <v>1.28567156954724</v>
       </c>
       <c r="D56" t="n">
-        <v>1.12579228083684</v>
+        <v>1.63113880111476</v>
       </c>
       <c r="E56" t="n">
-        <v>-1.26472340399153</v>
+        <v>-0.612254917978704</v>
       </c>
       <c r="F56" t="n">
-        <v>-1.56121729108957</v>
+        <v>-1.62105854822192</v>
       </c>
       <c r="G56" t="n">
-        <v>2.0967860437263</v>
+        <v>2.05601950328765</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>-0.589030743986746</v>
+        <v>-0.658031905677607</v>
       </c>
       <c r="B57" t="n">
-        <v>-1.04631753269669</v>
+        <v>-0.871669450147831</v>
       </c>
       <c r="C57" t="n">
-        <v>1.55964186564202</v>
+        <v>0.961325516832284</v>
       </c>
       <c r="D57" t="n">
-        <v>0.481634178307394</v>
+        <v>0.266749454872931</v>
       </c>
       <c r="E57" t="n">
-        <v>-1.63311131757702</v>
+        <v>-1.13893982444794</v>
       </c>
       <c r="F57" t="n">
-        <v>-1.98303597168071</v>
+        <v>-1.86811954706696</v>
       </c>
       <c r="G57" t="n">
-        <v>1.8816722978987</v>
+        <v>2.12626803297741</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>-0.774592741585992</v>
+        <v>-0.929635798904314</v>
       </c>
       <c r="B58" t="n">
-        <v>-1.11485527000865</v>
+        <v>-0.874202771098143</v>
       </c>
       <c r="C58" t="n">
-        <v>1.69156898534785</v>
+        <v>0.778574459887923</v>
       </c>
       <c r="D58" t="n">
-        <v>0.560323948488853</v>
+        <v>0.919097758019601</v>
       </c>
       <c r="E58" t="n">
-        <v>-1.14574805705369</v>
+        <v>-1.12280826561057</v>
       </c>
       <c r="F58" t="n">
-        <v>-1.6651316130868</v>
+        <v>-1.473902705676</v>
       </c>
       <c r="G58" t="n">
-        <v>1.99716607773464</v>
+        <v>2.13973517056823</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>-1.2026701825722</v>
+        <v>-0.81998421835189</v>
       </c>
       <c r="B59" t="n">
-        <v>-0.994229271055451</v>
+        <v>-1.14358195533132</v>
       </c>
       <c r="C59" t="n">
-        <v>1.65118541551146</v>
+        <v>1.29797433252119</v>
       </c>
       <c r="D59" t="n">
-        <v>1.54419948390892</v>
+        <v>0.723047433216619</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.634897732568444</v>
+        <v>-1.62973973507734</v>
       </c>
       <c r="F59" t="n">
-        <v>-1.18034702435957</v>
+        <v>-1.81424892008664</v>
       </c>
       <c r="G59" t="n">
-        <v>1.96666186132325</v>
+        <v>2.08096529543934</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>-1.10374994345115</v>
+        <v>-1.17733044665935</v>
       </c>
       <c r="B60" t="n">
-        <v>-1.03507792631147</v>
+        <v>-1.02415362820184</v>
       </c>
       <c r="C60" t="n">
-        <v>1.5543590433302</v>
+        <v>1.18995471712095</v>
       </c>
       <c r="D60" t="n">
-        <v>1.3652711378784</v>
+        <v>1.27721685649301</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.899684942719007</v>
+        <v>-0.882357258632933</v>
       </c>
       <c r="F60" t="n">
-        <v>-1.25145731879955</v>
+        <v>-1.27557137261183</v>
       </c>
       <c r="G60" t="n">
-        <v>2.0181548662972</v>
+        <v>2.07997889521612</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>-1.18884995492363</v>
+        <v>-0.964358305625759</v>
       </c>
       <c r="B61" t="n">
-        <v>-1.02906713549729</v>
+        <v>-1.08310580876376</v>
       </c>
       <c r="C61" t="n">
-        <v>1.54827685358848</v>
+        <v>1.36327408745249</v>
       </c>
       <c r="D61" t="n">
-        <v>1.27519432632734</v>
+        <v>0.773927371828267</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.801737302246035</v>
+        <v>-1.08671123376591</v>
       </c>
       <c r="F61" t="n">
-        <v>-1.73129521527493</v>
+        <v>-1.33556413261029</v>
       </c>
       <c r="G61" t="n">
-        <v>2.08061232851547</v>
+        <v>2.16130007863496</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>-1.04115595675449</v>
+        <v>-0.966633872264223</v>
       </c>
       <c r="B62" t="n">
-        <v>-1.1094555339702</v>
+        <v>-1.22736054713515</v>
       </c>
       <c r="C62" t="n">
-        <v>1.64566634854628</v>
+        <v>1.29936737543268</v>
       </c>
       <c r="D62" t="n">
-        <v>1.18216666229099</v>
+        <v>1.02983002931435</v>
       </c>
       <c r="E62" t="n">
-        <v>-1.02071816772738</v>
+        <v>-1.34083066402199</v>
       </c>
       <c r="F62" t="n">
-        <v>-1.37013329355065</v>
+        <v>-2.35730251227946</v>
       </c>
       <c r="G62" t="n">
-        <v>2.09680007901139</v>
+        <v>1.94087317659138</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>-1.02367692933909</v>
+        <v>-0.873065497063528</v>
       </c>
       <c r="B63" t="n">
-        <v>-1.04681345196793</v>
+        <v>-0.982131262379791</v>
       </c>
       <c r="C63" t="n">
-        <v>1.52287023713142</v>
+        <v>0.98882009393052</v>
       </c>
       <c r="D63" t="n">
-        <v>1.10851217687561</v>
+        <v>0.785620024710236</v>
       </c>
       <c r="E63" t="n">
-        <v>-1.10187168058581</v>
+        <v>-1.55933361142397</v>
       </c>
       <c r="F63" t="n">
-        <v>-1.50435774572116</v>
+        <v>-1.63193071291216</v>
       </c>
       <c r="G63" t="n">
-        <v>1.93991310238402</v>
+        <v>1.99322654083703</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>-0.842833177414937</v>
+        <v>-1.51361401504072</v>
       </c>
       <c r="B64" t="n">
-        <v>-1.02604738690718</v>
+        <v>-0.726002922821493</v>
       </c>
       <c r="C64" t="n">
-        <v>1.63237309706995</v>
+        <v>0.948544676057205</v>
       </c>
       <c r="D64" t="n">
-        <v>1.13029170699043</v>
+        <v>1.72196590494529</v>
       </c>
       <c r="E64" t="n">
-        <v>-1.22900985586596</v>
+        <v>-0.539562613322226</v>
       </c>
       <c r="F64" t="n">
-        <v>-1.78697046084215</v>
+        <v>-1.66076619180591</v>
       </c>
       <c r="G64" t="n">
-        <v>2.11521539998454</v>
+        <v>2.05235416915344</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>-1.07197504738286</v>
+        <v>-0.73976480605873</v>
       </c>
       <c r="B65" t="n">
-        <v>-0.909030419136852</v>
+        <v>-1.00875542953798</v>
       </c>
       <c r="C65" t="n">
-        <v>1.39381225821492</v>
+        <v>1.0881118734635</v>
       </c>
       <c r="D65" t="n">
-        <v>1.70656731243896</v>
+        <v>0.307654060492856</v>
       </c>
       <c r="E65" t="n">
-        <v>-1.08860096925961</v>
+        <v>-1.33713565915935</v>
       </c>
       <c r="F65" t="n">
-        <v>-1.58768460923701</v>
+        <v>-2.49704840655619</v>
       </c>
       <c r="G65" t="n">
-        <v>2.0952470485239</v>
+        <v>1.99900758798016</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>-0.818174114580191</v>
+        <v>-1.14886129152802</v>
       </c>
       <c r="B66" t="n">
-        <v>-0.88380313840454</v>
+        <v>-0.813272973784817</v>
       </c>
       <c r="C66" t="n">
-        <v>1.46058055073173</v>
+        <v>0.775497579190159</v>
       </c>
       <c r="D66" t="n">
-        <v>0.786249394188646</v>
+        <v>1.13647462325666</v>
       </c>
       <c r="E66" t="n">
-        <v>-1.08544028537495</v>
+        <v>-0.813463460744271</v>
       </c>
       <c r="F66" t="n">
-        <v>-1.70716177616088</v>
+        <v>-1.31758880439721</v>
       </c>
       <c r="G66" t="n">
-        <v>2.11145149447311</v>
+        <v>1.982818860405</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>-1.1142702623979</v>
+        <v>-1.17049407939309</v>
       </c>
       <c r="B67" t="n">
-        <v>-0.971788928131588</v>
+        <v>-0.832975118226927</v>
       </c>
       <c r="C67" t="n">
-        <v>1.46302740167288</v>
+        <v>0.853052334984061</v>
       </c>
       <c r="D67" t="n">
-        <v>1.19519260502742</v>
+        <v>1.21925287292164</v>
       </c>
       <c r="E67" t="n">
-        <v>-1.0215909992504</v>
+        <v>-1.03189446614449</v>
       </c>
       <c r="F67" t="n">
-        <v>-2.08004512335822</v>
+        <v>-1.26914932984462</v>
       </c>
       <c r="G67" t="n">
-        <v>2.01147413453692</v>
+        <v>2.02859223677637</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>-1.23864230885198</v>
+        <v>-1.03949671920783</v>
       </c>
       <c r="B68" t="n">
-        <v>-1.04380617259694</v>
+        <v>-1.0174029886554</v>
       </c>
       <c r="C68" t="n">
-        <v>1.73547726071244</v>
+        <v>1.0221379079494</v>
       </c>
       <c r="D68" t="n">
-        <v>1.36951998327131</v>
+        <v>0.874299542165078</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.884068903526963</v>
+        <v>-1.13279957785517</v>
       </c>
       <c r="F68" t="n">
-        <v>-1.89997198135743</v>
+        <v>-1.3085934750051</v>
       </c>
       <c r="G68" t="n">
-        <v>2.07018518467282</v>
+        <v>1.94146343498113</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>-1.17670338908373</v>
+        <v>-0.976226257124697</v>
       </c>
       <c r="B69" t="n">
-        <v>-0.892636395059102</v>
+        <v>-1.20872001340519</v>
       </c>
       <c r="C69" t="n">
-        <v>1.43565997184979</v>
+        <v>1.18505971375783</v>
       </c>
       <c r="D69" t="n">
-        <v>1.64156496576037</v>
+        <v>0.551115096041594</v>
       </c>
       <c r="E69" t="n">
-        <v>-1.16500471979684</v>
+        <v>-0.948331590506064</v>
       </c>
       <c r="F69" t="n">
-        <v>-2.17151725182666</v>
+        <v>-2.04765141252564</v>
       </c>
       <c r="G69" t="n">
-        <v>2.02760671443468</v>
+        <v>1.89268484290937</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>-0.999379737805517</v>
+        <v>-0.863301171720444</v>
       </c>
       <c r="B70" t="n">
-        <v>-1.01805854617529</v>
+        <v>-0.9157551335524</v>
       </c>
       <c r="C70" t="n">
-        <v>1.48875496874951</v>
+        <v>1.0751901537786</v>
       </c>
       <c r="D70" t="n">
-        <v>1.21819773543994</v>
+        <v>0.682626363835499</v>
       </c>
       <c r="E70" t="n">
-        <v>-1.26680074322964</v>
+        <v>-1.13274995250348</v>
       </c>
       <c r="F70" t="n">
-        <v>-2.15308061203782</v>
+        <v>-1.54462302339955</v>
       </c>
       <c r="G70" t="n">
-        <v>2.02369469618088</v>
+        <v>2.00677386735197</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>-1.0779232769535</v>
+        <v>-0.850542602654094</v>
       </c>
       <c r="B71" t="n">
-        <v>-0.832147085672267</v>
+        <v>-0.83204013960777</v>
       </c>
       <c r="C71" t="n">
-        <v>1.39208134484519</v>
+        <v>1.01177189575539</v>
       </c>
       <c r="D71" t="n">
-        <v>1.42524932920266</v>
+        <v>0.760435414559958</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.830470727710726</v>
+        <v>-1.45589191880694</v>
       </c>
       <c r="F71" t="n">
-        <v>-1.38684492229763</v>
+        <v>-1.29669563832039</v>
       </c>
       <c r="G71" t="n">
-        <v>2.11150930128948</v>
+        <v>-1.74087634960006</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>-1.36492637062387</v>
+        <v>-1.33912741727345</v>
       </c>
       <c r="B72" t="n">
-        <v>-1.05554456354021</v>
+        <v>-1.1248667814972</v>
       </c>
       <c r="C72" t="n">
-        <v>1.49669722485668</v>
+        <v>1.2454751635247</v>
       </c>
       <c r="D72" t="n">
-        <v>1.95980491267479</v>
+        <v>1.46046644920256</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.518091702331452</v>
+        <v>-0.680093707274396</v>
       </c>
       <c r="F72" t="n">
-        <v>-1.11536972272098</v>
+        <v>-1.04869609715977</v>
       </c>
       <c r="G72" t="n">
-        <v>1.93764269509485</v>
+        <v>1.96850426922889</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>-1.16675712907549</v>
+        <v>-1.17355320332846</v>
       </c>
       <c r="B73" t="n">
-        <v>-0.73213605754403</v>
+        <v>-0.888807418141076</v>
       </c>
       <c r="C73" t="n">
-        <v>1.36335195767251</v>
+        <v>0.905397138328135</v>
       </c>
       <c r="D73" t="n">
-        <v>1.71763198649169</v>
+        <v>1.26719143859984</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.12804152236815</v>
+        <v>-0.983155293087516</v>
       </c>
       <c r="F73" t="n">
-        <v>-2.16966247346372</v>
+        <v>-2.12348004105432</v>
       </c>
       <c r="G73" t="n">
-        <v>2.13774933792361</v>
+        <v>2.0244703978717</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>-0.919036136597598</v>
+        <v>-0.746073700195733</v>
       </c>
       <c r="B74" t="n">
-        <v>-0.876896219438743</v>
+        <v>-1.02715396359254</v>
       </c>
       <c r="C74" t="n">
-        <v>1.35400847312442</v>
+        <v>1.12756740102846</v>
       </c>
       <c r="D74" t="n">
-        <v>0.976884068280692</v>
+        <v>0.770478527572876</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.30465294636046</v>
+        <v>-1.7847363316209</v>
       </c>
       <c r="F74" t="n">
-        <v>-1.5651304867624</v>
+        <v>-2.92113493362223</v>
       </c>
       <c r="G74" t="n">
-        <v>2.16744141531491</v>
+        <v>1.92817620369759</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>-0.894056504025863</v>
+        <v>-1.11327673311864</v>
       </c>
       <c r="B75" t="n">
-        <v>-0.609394024736996</v>
+        <v>-1.13130038519348</v>
       </c>
       <c r="C75" t="n">
-        <v>1.11736949575893</v>
+        <v>1.13675179126727</v>
       </c>
       <c r="D75" t="n">
-        <v>0.997113541160847</v>
+        <v>1.26209180535959</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.09546948023146</v>
+        <v>-1.53698990573335</v>
       </c>
       <c r="F75" t="n">
-        <v>-1.5878233296381</v>
+        <v>-1.41425558524052</v>
       </c>
       <c r="G75" t="n">
-        <v>2.06002884868465</v>
+        <v>1.94445053466495</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>-1.04598579561026</v>
+        <v>-0.959874909310266</v>
       </c>
       <c r="B76" t="n">
-        <v>-0.937004740468365</v>
+        <v>-0.993706400602262</v>
       </c>
       <c r="C76" t="n">
-        <v>1.4222712670119</v>
+        <v>1.08767419909302</v>
       </c>
       <c r="D76" t="n">
-        <v>1.3043268675483</v>
+        <v>0.820220389085818</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.19043951257567</v>
+        <v>-1.23909913171671</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.576249961279</v>
+        <v>-2.32810838463829</v>
       </c>
       <c r="G76" t="n">
-        <v>2.1085909418615</v>
+        <v>2.02867370953126</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>-1.3098460177561</v>
+        <v>-1.02520218684397</v>
       </c>
       <c r="B77" t="n">
-        <v>-0.897832472411326</v>
+        <v>-1.07621965169765</v>
       </c>
       <c r="C77" t="n">
-        <v>1.4255573644919</v>
+        <v>1.12264893927896</v>
       </c>
       <c r="D77" t="n">
-        <v>1.81280709740133</v>
+        <v>0.961973372801651</v>
       </c>
       <c r="E77" t="n">
-        <v>-0.976558391500919</v>
+        <v>-0.997927647380393</v>
       </c>
       <c r="F77" t="n">
-        <v>-2.01101637825535</v>
+        <v>-1.39960217072256</v>
       </c>
       <c r="G77" t="n">
-        <v>2.04673076371164</v>
+        <v>1.93273969633264</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>-1.055977635158</v>
+        <v>-1.18128380921375</v>
       </c>
       <c r="B78" t="n">
-        <v>-0.945522823579577</v>
+        <v>-0.795519174715203</v>
       </c>
       <c r="C78" t="n">
-        <v>1.46226030999077</v>
+        <v>0.785718752689216</v>
       </c>
       <c r="D78" t="n">
-        <v>1.38589443768849</v>
+        <v>1.28794138608986</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.12252456754646</v>
+        <v>-0.992867411916587</v>
       </c>
       <c r="F78" t="n">
-        <v>-1.53787439382376</v>
+        <v>-1.26805851210926</v>
       </c>
       <c r="G78" t="n">
-        <v>2.05414762462126</v>
+        <v>1.97149330996533</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>-0.985609737383835</v>
+        <v>-1.08469123638821</v>
       </c>
       <c r="B79" t="n">
-        <v>-0.830446270747687</v>
+        <v>-0.822078780112069</v>
       </c>
       <c r="C79" t="n">
-        <v>1.32292153950586</v>
+        <v>0.755790257553906</v>
       </c>
       <c r="D79" t="n">
-        <v>1.32509477047464</v>
+        <v>1.02058565638906</v>
       </c>
       <c r="E79" t="n">
-        <v>-1.13661936328224</v>
+        <v>-1.02339100934169</v>
       </c>
       <c r="F79" t="n">
-        <v>-1.58677973995359</v>
+        <v>-1.35099166034651</v>
       </c>
       <c r="G79" t="n">
-        <v>2.09297365607493</v>
+        <v>1.98589210378127</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>-1.05976959413258</v>
+        <v>-1.23967332824986</v>
       </c>
       <c r="B80" t="n">
-        <v>-1.02767433710588</v>
+        <v>-1.02386780419456</v>
       </c>
       <c r="C80" t="n">
-        <v>1.66797500444688</v>
+        <v>0.998740914075143</v>
       </c>
       <c r="D80" t="n">
-        <v>1.39277103129443</v>
+        <v>1.50123018098943</v>
       </c>
       <c r="E80" t="n">
-        <v>-0.839697838929163</v>
+        <v>-0.691539824664876</v>
       </c>
       <c r="F80" t="n">
-        <v>-1.46029315248852</v>
+        <v>-1.18054695501406</v>
       </c>
       <c r="G80" t="n">
-        <v>2.09242288714991</v>
+        <v>2.00189644621013</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>-1.07601879534772</v>
+        <v>-1.21081319902228</v>
       </c>
       <c r="B81" t="n">
-        <v>-0.837118381230926</v>
+        <v>-0.953373071722531</v>
       </c>
       <c r="C81" t="n">
-        <v>1.39238287276541</v>
+        <v>1.10588038368071</v>
       </c>
       <c r="D81" t="n">
-        <v>1.4939317131176</v>
+        <v>1.26167230433269</v>
       </c>
       <c r="E81" t="n">
-        <v>-0.8517066432496</v>
+        <v>-0.739555388662272</v>
       </c>
       <c r="F81" t="n">
-        <v>-1.53097593972999</v>
+        <v>-1.06558861294988</v>
       </c>
       <c r="G81" t="n">
-        <v>2.06539973977151</v>
+        <v>2.09994954272801</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>-0.852894528393686</v>
+        <v>-1.07128443114003</v>
       </c>
       <c r="B82" t="n">
-        <v>-0.879335383654078</v>
+        <v>-0.830444478136243</v>
       </c>
       <c r="C82" t="n">
-        <v>1.54788786876058</v>
+        <v>0.83949304847316</v>
       </c>
       <c r="D82" t="n">
-        <v>0.924676887759807</v>
+        <v>1.2580206614658</v>
       </c>
       <c r="E82" t="n">
-        <v>-1.3731161563851</v>
+        <v>-1.43290749172532</v>
       </c>
       <c r="F82" t="n">
-        <v>-1.60256810588634</v>
+        <v>-1.45003585697689</v>
       </c>
       <c r="G82" t="n">
-        <v>2.17764313105664</v>
+        <v>2.09994515932382</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>-1.01990442806983</v>
+        <v>-1.03717067777801</v>
       </c>
       <c r="B83" t="n">
-        <v>-1.06041808023388</v>
+        <v>-1.32185435491443</v>
       </c>
       <c r="C83" t="n">
-        <v>1.57999392197243</v>
+        <v>1.45053953952059</v>
       </c>
       <c r="D83" t="n">
-        <v>1.26277457909761</v>
+        <v>0.98914166811687</v>
       </c>
       <c r="E83" t="n">
-        <v>-1.25659318803091</v>
+        <v>-1.10832850499205</v>
       </c>
       <c r="F83" t="n">
-        <v>-2.1738363164735</v>
+        <v>-2.00481561777492</v>
       </c>
       <c r="G83" t="n">
-        <v>2.20130991986509</v>
+        <v>1.9755395644174</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>-1.098510548874</v>
+        <v>-0.665261995925318</v>
       </c>
       <c r="B84" t="n">
-        <v>-1.06379037036603</v>
+        <v>-0.88121316147044</v>
       </c>
       <c r="C84" t="n">
-        <v>1.54862800905141</v>
+        <v>0.955392875771908</v>
       </c>
       <c r="D84" t="n">
-        <v>1.14792679126646</v>
+        <v>0.473439841370272</v>
       </c>
       <c r="E84" t="n">
-        <v>-0.910194108714299</v>
+        <v>-1.47263464968606</v>
       </c>
       <c r="F84" t="n">
-        <v>-1.96143097088397</v>
+        <v>-1.87228770530566</v>
       </c>
       <c r="G84" t="n">
-        <v>2.08633847819059</v>
+        <v>1.9968795449622</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>-1.07875740577208</v>
+        <v>-0.723805648663511</v>
       </c>
       <c r="B85" t="n">
-        <v>-0.993576321252754</v>
+        <v>-0.88659764978582</v>
       </c>
       <c r="C85" t="n">
-        <v>1.66130439720432</v>
+        <v>0.960859682609738</v>
       </c>
       <c r="D85" t="n">
-        <v>1.30259357911704</v>
+        <v>0.502911555758187</v>
       </c>
       <c r="E85" t="n">
-        <v>-1.06377880698905</v>
+        <v>-1.47091755316475</v>
       </c>
       <c r="F85" t="n">
-        <v>-2.00273826221275</v>
+        <v>-2.54601393727912</v>
       </c>
       <c r="G85" t="n">
-        <v>1.99727312187796</v>
+        <v>2.1178131620048</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>-1.07035031859654</v>
+        <v>-1.19957018324552</v>
       </c>
       <c r="B86" t="n">
-        <v>-0.987051531429325</v>
+        <v>-1.07322920668873</v>
       </c>
       <c r="C86" t="n">
-        <v>1.6780187417932</v>
+        <v>1.29728366811925</v>
       </c>
       <c r="D86" t="n">
-        <v>1.42250090649721</v>
+        <v>1.32090468076974</v>
       </c>
       <c r="E86" t="n">
-        <v>-0.754989621677431</v>
+        <v>-0.988226786939562</v>
       </c>
       <c r="F86" t="n">
-        <v>-1.54281444581211</v>
+        <v>-1.92693830148691</v>
       </c>
       <c r="G86" t="n">
-        <v>2.05083957278879</v>
+        <v>2.07872123779243</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>-1.05853635537663</v>
+        <v>-1.03867430136542</v>
       </c>
       <c r="B87" t="n">
-        <v>-1.01084142401286</v>
+        <v>-1.06535572576099</v>
       </c>
       <c r="C87" t="n">
-        <v>1.5800046536548</v>
+        <v>1.01440149159348</v>
       </c>
       <c r="D87" t="n">
-        <v>1.26298599597885</v>
+        <v>0.961156294343471</v>
       </c>
       <c r="E87" t="n">
-        <v>-0.931975454430491</v>
+        <v>-0.693255506389395</v>
       </c>
       <c r="F87" t="n">
-        <v>-1.45768828980001</v>
+        <v>-1.22895518059642</v>
       </c>
       <c r="G87" t="n">
-        <v>2.03074853866721</v>
+        <v>2.0864793717391</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>-1.05524860704935</v>
+        <v>-1.18316047853272</v>
       </c>
       <c r="B88" t="n">
-        <v>-1.19807804305955</v>
+        <v>-1.32418753551582</v>
       </c>
       <c r="C88" t="n">
-        <v>1.78598752095191</v>
+        <v>1.31482286330315</v>
       </c>
       <c r="D88" t="n">
-        <v>0.99308120956208</v>
+        <v>0.992603592754842</v>
       </c>
       <c r="E88" t="n">
-        <v>-1.06227782887784</v>
+        <v>-0.761386425191933</v>
       </c>
       <c r="F88" t="n">
-        <v>-1.88682827455094</v>
+        <v>-1.02297158903311</v>
       </c>
       <c r="G88" t="n">
-        <v>2.13978952412334</v>
+        <v>1.90472214654691</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>-1.16417903356697</v>
+        <v>-1.06424428634975</v>
       </c>
       <c r="B89" t="n">
-        <v>-0.920707967900799</v>
+        <v>-0.844459338905005</v>
       </c>
       <c r="C89" t="n">
-        <v>1.548677725301</v>
+        <v>0.909305672702464</v>
       </c>
       <c r="D89" t="n">
-        <v>1.55664288349153</v>
+        <v>1.18155118040731</v>
       </c>
       <c r="E89" t="n">
-        <v>-0.762626572707199</v>
+        <v>-1.19654740747807</v>
       </c>
       <c r="F89" t="n">
-        <v>-1.32028831649162</v>
+        <v>-1.45215963531563</v>
       </c>
       <c r="G89" t="n">
-        <v>2.12445810945886</v>
+        <v>2.11970058058498</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>-0.957713703377915</v>
+        <v>-1.21990663003378</v>
       </c>
       <c r="B90" t="n">
-        <v>-0.734506127079617</v>
+        <v>-1.02469571071847</v>
       </c>
       <c r="C90" t="n">
-        <v>1.17181387473657</v>
+        <v>0.943894989916145</v>
       </c>
       <c r="D90" t="n">
-        <v>1.22765476995223</v>
+        <v>1.2330146101943</v>
       </c>
       <c r="E90" t="n">
-        <v>-0.789542507013811</v>
+        <v>-0.587373645180829</v>
       </c>
       <c r="F90" t="n">
-        <v>-1.67166922356388</v>
+        <v>-1.05870879343507</v>
       </c>
       <c r="G90" t="n">
-        <v>2.07401969366495</v>
+        <v>2.0315201616357</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>-1.15078523508981</v>
+        <v>-1.10786733184507</v>
       </c>
       <c r="B91" t="n">
-        <v>-0.977613227632446</v>
+        <v>-1.04796713127069</v>
       </c>
       <c r="C91" t="n">
-        <v>1.41572335669242</v>
+        <v>1.06054040143948</v>
       </c>
       <c r="D91" t="n">
-        <v>1.38428205966579</v>
+        <v>1.03907993564628</v>
       </c>
       <c r="E91" t="n">
-        <v>-1.01286688744158</v>
+        <v>-1.00366738361686</v>
       </c>
       <c r="F91" t="n">
-        <v>-1.22648758153124</v>
+        <v>-1.26352954381447</v>
       </c>
       <c r="G91" t="n">
-        <v>1.91293778281939</v>
+        <v>2.07062767864752</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>-1.16727904733192</v>
+        <v>-0.912078146068248</v>
       </c>
       <c r="B92" t="n">
-        <v>-1.14403103696712</v>
+        <v>-0.994657213567918</v>
       </c>
       <c r="C92" t="n">
-        <v>1.80236752208728</v>
+        <v>1.05792419077893</v>
       </c>
       <c r="D92" t="n">
-        <v>1.37783578457345</v>
+        <v>0.674504731489129</v>
       </c>
       <c r="E92" t="n">
-        <v>-0.634674658290124</v>
+        <v>-1.02484118332424</v>
       </c>
       <c r="F92" t="n">
-        <v>-1.30360915572558</v>
+        <v>-1.55255414371079</v>
       </c>
       <c r="G92" t="n">
-        <v>2.0475572124748</v>
+        <v>2.00109799076392</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>-1.09257289184134</v>
+        <v>-0.953855700719467</v>
       </c>
       <c r="B93" t="n">
-        <v>-1.0513657312615</v>
+        <v>-0.884326376563555</v>
       </c>
       <c r="C93" t="n">
-        <v>1.67221458472087</v>
+        <v>0.801114129870718</v>
       </c>
       <c r="D93" t="n">
-        <v>1.05950427806287</v>
+        <v>1.07579988382292</v>
       </c>
       <c r="E93" t="n">
-        <v>-1.06539348034315</v>
+        <v>-1.18346740363605</v>
       </c>
       <c r="F93" t="n">
-        <v>-1.35478547436666</v>
+        <v>-1.65812735491235</v>
       </c>
       <c r="G93" t="n">
-        <v>2.00750548766286</v>
+        <v>1.99252014392637</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>-1.06166626216135</v>
+        <v>-0.955168165161738</v>
       </c>
       <c r="B94" t="n">
-        <v>-1.18906306359377</v>
+        <v>-0.764911483195696</v>
       </c>
       <c r="C94" t="n">
-        <v>1.61941444320641</v>
+        <v>0.803830170873521</v>
       </c>
       <c r="D94" t="n">
-        <v>1.38099379205071</v>
+        <v>1.13019188079179</v>
       </c>
       <c r="E94" t="n">
-        <v>-0.977662420317007</v>
+        <v>-1.08830140267684</v>
       </c>
       <c r="F94" t="n">
-        <v>-1.57652478264547</v>
+        <v>-1.75060916485918</v>
       </c>
       <c r="G94" t="n">
-        <v>2.01990484377995</v>
+        <v>1.9535060737859</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>-1.07018181867518</v>
+        <v>-0.852530447474243</v>
       </c>
       <c r="B95" t="n">
-        <v>-1.02205848877281</v>
+        <v>-0.93932012289632</v>
       </c>
       <c r="C95" t="n">
-        <v>1.8698271437006</v>
+        <v>0.96236713333396</v>
       </c>
       <c r="D95" t="n">
-        <v>1.32859351092578</v>
+        <v>0.547898882215523</v>
       </c>
       <c r="E95" t="n">
-        <v>-1.15961702004996</v>
+        <v>-1.14532814390649</v>
       </c>
       <c r="F95" t="n">
-        <v>-1.9770293153132</v>
+        <v>-1.58004313802643</v>
       </c>
       <c r="G95" t="n">
-        <v>2.11244688626738</v>
+        <v>1.9785038265535</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>-1.12404732339247</v>
+        <v>-0.726536635211527</v>
       </c>
       <c r="B96" t="n">
-        <v>-0.93565783148503</v>
+        <v>-0.906029435466261</v>
       </c>
       <c r="C96" t="n">
-        <v>1.37412451008481</v>
+        <v>0.897651839396501</v>
       </c>
       <c r="D96" t="n">
-        <v>1.08022186818333</v>
+        <v>0.58796035153429</v>
       </c>
       <c r="E96" t="n">
-        <v>-0.736014757975345</v>
+        <v>-1.49221336520556</v>
       </c>
       <c r="F96" t="n">
-        <v>-1.20883150937517</v>
+        <v>-1.90894789150043</v>
       </c>
       <c r="G96" t="n">
-        <v>1.88176846305927</v>
+        <v>2.02820856719433</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>-1.0417721722095</v>
+        <v>-1.53327799431942</v>
       </c>
       <c r="B97" t="n">
-        <v>-0.721670631879607</v>
+        <v>-1.35609255401126</v>
       </c>
       <c r="C97" t="n">
-        <v>1.20539497142834</v>
+        <v>1.55820096826111</v>
       </c>
       <c r="D97" t="n">
-        <v>1.20448198080135</v>
+        <v>1.43892088200168</v>
       </c>
       <c r="E97" t="n">
-        <v>-1.13940247964023</v>
+        <v>-0.131273951841241</v>
       </c>
       <c r="F97" t="n">
-        <v>-1.41846690257197</v>
+        <v>-0.618867969332027</v>
       </c>
       <c r="G97" t="n">
-        <v>1.92171807662552</v>
+        <v>1.95309304491943</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>-1.0821988042695</v>
+        <v>-0.62984543929735</v>
       </c>
       <c r="B98" t="n">
-        <v>-1.00780382260033</v>
+        <v>-0.993017254784851</v>
       </c>
       <c r="C98" t="n">
-        <v>1.52379018567536</v>
+        <v>1.0771941487253</v>
       </c>
       <c r="D98" t="n">
-        <v>1.34635366782956</v>
+        <v>0.281030772037648</v>
       </c>
       <c r="E98" t="n">
-        <v>-1.15513734980862</v>
+        <v>-1.65096647876083</v>
       </c>
       <c r="F98" t="n">
-        <v>-1.41698993239215</v>
+        <v>-2.71724766987301</v>
       </c>
       <c r="G98" t="n">
-        <v>1.97961872525759</v>
+        <v>1.98357438973154</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>-1.16676086487418</v>
+        <v>-1.40417501587047</v>
       </c>
       <c r="B99" t="n">
-        <v>-0.99557256887927</v>
+        <v>-0.911555389999721</v>
       </c>
       <c r="C99" t="n">
-        <v>1.46293752535484</v>
+        <v>0.850295790297756</v>
       </c>
       <c r="D99" t="n">
-        <v>1.51057664664247</v>
+        <v>1.49954167514103</v>
       </c>
       <c r="E99" t="n">
-        <v>-0.925175222879886</v>
+        <v>-0.34695527530866</v>
       </c>
       <c r="F99" t="n">
-        <v>-1.33122419946385</v>
+        <v>-0.808166160380812</v>
       </c>
       <c r="G99" t="n">
-        <v>2.04039248798164</v>
+        <v>2.03930401610528</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>-1.18776298321106</v>
+        <v>-1.01655294602264</v>
       </c>
       <c r="B100" t="n">
-        <v>-1.03692318723345</v>
+        <v>-0.992372206482225</v>
       </c>
       <c r="C100" t="n">
-        <v>1.81192162017954</v>
+        <v>1.14011444237404</v>
       </c>
       <c r="D100" t="n">
-        <v>1.56613435153418</v>
+        <v>0.816871215361253</v>
       </c>
       <c r="E100" t="n">
-        <v>-0.953642474620582</v>
+        <v>-0.637865107373904</v>
       </c>
       <c r="F100" t="n">
-        <v>-1.91065281712018</v>
+        <v>-1.35026733651116</v>
       </c>
       <c r="G100" t="n">
-        <v>2.09694644812656</v>
+        <v>2.08154612923722</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>-1.00966205522337</v>
+        <v>-1.10760999011219</v>
       </c>
       <c r="B101" t="n">
-        <v>-1.06536314395363</v>
+        <v>-0.894084205481966</v>
       </c>
       <c r="C101" t="n">
-        <v>1.47018304967757</v>
+        <v>1.00433647891382</v>
       </c>
       <c r="D101" t="n">
-        <v>1.15859211050306</v>
+        <v>1.12531517987591</v>
       </c>
       <c r="E101" t="n">
-        <v>-0.970997851494461</v>
+        <v>-0.585362026878755</v>
       </c>
       <c r="F101" t="n">
-        <v>-1.40920293414088</v>
+        <v>-1.25021917676799</v>
       </c>
       <c r="G101" t="n">
-        <v>2.0177950529185</v>
+        <v>2.05032902158797</v>
       </c>
     </row>
   </sheetData>
@@ -3146,826 +3149,826 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4.51080689990923</v>
+        <v>10.8536866098677</v>
       </c>
       <c r="B2" t="n">
-        <v>0.331382806449163</v>
+        <v>0.48276298932135</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>8.28173199783536</v>
+        <v>5.10947142017131</v>
       </c>
       <c r="B3" t="n">
-        <v>0.381850018831216</v>
+        <v>0.311415863294082</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>13.5492819296638</v>
+        <v>0.526642888538798</v>
       </c>
       <c r="B4" t="n">
-        <v>0.3790529085696</v>
+        <v>0.270919815913449</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2.29799312132359</v>
+        <v>3.90098940730297</v>
       </c>
       <c r="B5" t="n">
-        <v>0.247515520336661</v>
+        <v>0.308233108093842</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.0608538912039886</v>
+        <v>0.101249356622365</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0649056126783284</v>
+        <v>0.0925722586018904</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18.0512177338194</v>
+        <v>2.86503042281403</v>
       </c>
       <c r="B7" t="n">
-        <v>0.417947167020949</v>
+        <v>0.2727956759729</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.107922364601146</v>
+        <v>1.79435259180013</v>
       </c>
       <c r="B8" t="n">
-        <v>0.199373960741914</v>
+        <v>0.44991647742916</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.264475398892823</v>
+        <v>0.23900480929141</v>
       </c>
       <c r="B9" t="n">
-        <v>0.0996450487346623</v>
+        <v>0.23739164155926</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>15.4864829424999</v>
+        <v>19.9769069393179</v>
       </c>
       <c r="B10" t="n">
-        <v>0.40438645764363</v>
+        <v>0.402298852163172</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.174398277265839</v>
+        <v>4.49594749055865</v>
       </c>
       <c r="B11" t="n">
-        <v>0.288602001696766</v>
+        <v>0.316336661717379</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.128194379927095</v>
+        <v>2.77033177377385</v>
       </c>
       <c r="B12" t="n">
-        <v>0.0479595913486883</v>
+        <v>0.271085559103465</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1.37654012942667</v>
+        <v>12.3224622433258</v>
       </c>
       <c r="B13" t="n">
-        <v>0.204145931608948</v>
+        <v>0.388942248405645</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2.10322681934234</v>
+        <v>2.76142147379249</v>
       </c>
       <c r="B14" t="n">
-        <v>0.252142193183831</v>
+        <v>0.277096952175504</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>10.4877774049239</v>
+        <v>0.78658893009542</v>
       </c>
       <c r="B15" t="n">
-        <v>0.385763007718574</v>
+        <v>0.220036320636819</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.332852997221454</v>
+        <v>0.154984856691229</v>
       </c>
       <c r="B16" t="n">
-        <v>0.0816555638070898</v>
+        <v>0.43772494629863</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.257724438631249</v>
+        <v>0.389077157349189</v>
       </c>
       <c r="B17" t="n">
-        <v>0.257801953798104</v>
+        <v>0.118428516231175</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.981166805329194</v>
+        <v>0.52284620875953</v>
       </c>
       <c r="B18" t="n">
-        <v>0.189034454074733</v>
+        <v>0.105557922050502</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.174110829496288</v>
+        <v>21.0024014533944</v>
       </c>
       <c r="B19" t="n">
-        <v>0.294834061990286</v>
+        <v>0.420292969763915</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.59473404961179</v>
+        <v>1.71412574075374</v>
       </c>
       <c r="B20" t="n">
-        <v>0.142982587165679</v>
+        <v>0.219257516562686</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1.65163361469276</v>
+        <v>2.14485301610932</v>
       </c>
       <c r="B21" t="n">
-        <v>0.261432902699977</v>
+        <v>0.231813165372222</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0.81411346543393</v>
+        <v>2.24999263784558</v>
       </c>
       <c r="B22" t="n">
-        <v>0.184220371262792</v>
+        <v>0.281860167640917</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>0.493188699389312</v>
+        <v>2.68515726064998</v>
       </c>
       <c r="B23" t="n">
-        <v>0.135251774446473</v>
+        <v>0.260261738688829</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>3.22169885408828</v>
+        <v>0.374606448953253</v>
       </c>
       <c r="B24" t="n">
-        <v>0.478095642808929</v>
+        <v>0.119765988770649</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0.45514579105591</v>
+        <v>133.905319429654</v>
       </c>
       <c r="B25" t="n">
-        <v>0.146525187953475</v>
+        <v>0.576830786492576</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0.626450642696881</v>
+        <v>0.14664920987666</v>
       </c>
       <c r="B26" t="n">
-        <v>0.157644805148364</v>
+        <v>0.306823792418331</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>88.6997553485973</v>
+        <v>0.242750061533867</v>
       </c>
       <c r="B27" t="n">
-        <v>0.516116739094664</v>
+        <v>0.218118905507916</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0.0532182775534556</v>
+        <v>0.149688140372573</v>
       </c>
       <c r="B28" t="n">
-        <v>0.0625331423324681</v>
+        <v>0.316225696898697</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1.86206209471908</v>
+        <v>8.71872912654143</v>
       </c>
       <c r="B29" t="n">
-        <v>0.223609733818246</v>
+        <v>0.346225362305168</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0.148923492085395</v>
+        <v>29.1056097012947</v>
       </c>
       <c r="B30" t="n">
-        <v>0.116849055805801</v>
+        <v>0.451833344643702</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>109.166265362831</v>
+        <v>0.152319832382669</v>
       </c>
       <c r="B31" t="n">
-        <v>0.538055975700243</v>
+        <v>0.0629426269678059</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0.613869022356015</v>
+        <v>0.170776859027821</v>
       </c>
       <c r="B32" t="n">
-        <v>0.141270881272622</v>
+        <v>0.144446590513599</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>26.7915802384579</v>
+        <v>20.1862769958514</v>
       </c>
       <c r="B33" t="n">
-        <v>0.454528522853101</v>
+        <v>0.406800964806277</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>16.0584430214164</v>
+        <v>25.7599174171518</v>
       </c>
       <c r="B34" t="n">
-        <v>0.395303179762666</v>
+        <v>0.433703386159357</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>10.622667880437</v>
+        <v>0.788969840747031</v>
       </c>
       <c r="B35" t="n">
-        <v>0.354598287738399</v>
+        <v>0.163095128450728</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>5.57062915343512</v>
+        <v>0.374266780279234</v>
       </c>
       <c r="B36" t="n">
-        <v>0.31608684198172</v>
+        <v>0.120769246575578</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1.05738599147437</v>
+        <v>14.2849013744923</v>
       </c>
       <c r="B37" t="n">
-        <v>0.363473471515798</v>
+        <v>0.382774606179405</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1.38106923108399</v>
+        <v>0.175370598985803</v>
       </c>
       <c r="B38" t="n">
-        <v>0.211516191601578</v>
+        <v>0.425406500527771</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1.58515346308053</v>
+        <v>0.287838044302473</v>
       </c>
       <c r="B39" t="n">
-        <v>0.215212887052706</v>
+        <v>0.260358532284706</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1.12473592556645</v>
+        <v>24.7957480162655</v>
       </c>
       <c r="B40" t="n">
-        <v>0.190900080208099</v>
+        <v>0.430835978300324</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1.40136036361939</v>
+        <v>0.406220388169796</v>
       </c>
       <c r="B41" t="n">
-        <v>0.213673689836047</v>
+        <v>0.115373089409251</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>13.3128275880007</v>
+        <v>26.6453562045927</v>
       </c>
       <c r="B42" t="n">
-        <v>0.391689844246873</v>
+        <v>0.443751703417307</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>41.7167411717811</v>
+        <v>6.06142869027426</v>
       </c>
       <c r="B43" t="n">
-        <v>0.484831145828612</v>
+        <v>0.323419776262001</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>0.132001313647227</v>
+        <v>6.05749356602858</v>
       </c>
       <c r="B44" t="n">
-        <v>0.0991956558394785</v>
+        <v>0.311211525363721</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>0.20233118001814</v>
+        <v>5.55962023748983</v>
       </c>
       <c r="B45" t="n">
-        <v>0.0808448068062736</v>
+        <v>0.322081103760053</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>0.872903392985843</v>
+        <v>63.3822438291413</v>
       </c>
       <c r="B46" t="n">
-        <v>0.209153512674762</v>
+        <v>0.515446538046788</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>0.209270118297417</v>
+        <v>13.8415755239412</v>
       </c>
       <c r="B47" t="n">
-        <v>0.0619331158497464</v>
+        <v>0.39167505560742</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>2.61370820386223</v>
+        <v>0.236451703972231</v>
       </c>
       <c r="B48" t="n">
-        <v>0.258824050432143</v>
+        <v>0.0515843972612784</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>5.07172000013882</v>
+        <v>5.35598473556392</v>
       </c>
       <c r="B49" t="n">
-        <v>0.299402860263981</v>
+        <v>0.295648125205757</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>0.103519575774647</v>
+        <v>17.2437082991254</v>
       </c>
       <c r="B50" t="n">
-        <v>0.0823709046030855</v>
+        <v>0.418915086415038</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>24.6732600835611</v>
+        <v>27.8599956234462</v>
       </c>
       <c r="B51" t="n">
-        <v>0.406765478558516</v>
+        <v>0.450965458651929</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>2.15332331591913</v>
+        <v>1.21543828935999</v>
       </c>
       <c r="B52" t="n">
-        <v>0.240588342785254</v>
+        <v>0.210926924872297</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>48.1855213060782</v>
+        <v>0.498408701510584</v>
       </c>
       <c r="B53" t="n">
-        <v>0.504888411533077</v>
+        <v>0.143591814934612</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>0.502412848738865</v>
+        <v>0.61381062825776</v>
       </c>
       <c r="B54" t="n">
-        <v>0.136797837245979</v>
+        <v>0.157220575936571</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>0.29725596996866</v>
+        <v>11.7301817758416</v>
       </c>
       <c r="B55" t="n">
-        <v>0.107850500755969</v>
+        <v>0.405425003127906</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>4.72177442085466</v>
+        <v>0.37501747485369</v>
       </c>
       <c r="B56" t="n">
-        <v>0.326911368410165</v>
+        <v>0.306981127882032</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>142.869167520454</v>
+        <v>79.1946898729113</v>
       </c>
       <c r="B57" t="n">
-        <v>0.557410272113862</v>
+        <v>0.516830195673312</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>10.6056781394851</v>
+        <v>3.50469576879721</v>
       </c>
       <c r="B58" t="n">
-        <v>0.391873221624293</v>
+        <v>0.274395379488067</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>0.101574562397442</v>
+        <v>27.2768563365133</v>
       </c>
       <c r="B59" t="n">
-        <v>0.0424487514395053</v>
+        <v>0.475270033845656</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>0.483123018897135</v>
+        <v>0.479947713736338</v>
       </c>
       <c r="B60" t="n">
-        <v>0.107795704467016</v>
+        <v>0.117388657348865</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>0.242005419857478</v>
+        <v>0.894166172094228</v>
       </c>
       <c r="B61" t="n">
-        <v>0.206115958873677</v>
+        <v>0.178614785369752</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>0.652312465861389</v>
+        <v>3.00889826789285</v>
       </c>
       <c r="B62" t="n">
-        <v>0.179534313253598</v>
+        <v>0.427233140708247</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>3.9993932175568</v>
+        <v>17.2961886226372</v>
       </c>
       <c r="B63" t="n">
-        <v>0.290594876548132</v>
+        <v>0.406425717158071</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>20.8458181736077</v>
+        <v>0.157349483425541</v>
       </c>
       <c r="B64" t="n">
-        <v>0.458877614161839</v>
+        <v>0.230742521028709</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>10.5245497226331</v>
+        <v>3.10035834942128</v>
       </c>
       <c r="B65" t="n">
-        <v>0.355332572685001</v>
+        <v>0.440255968639426</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>19.6621520470542</v>
+        <v>0.379928154574337</v>
       </c>
       <c r="B66" t="n">
-        <v>0.423842863015617</v>
+        <v>0.133986683855454</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>0.196191436179892</v>
+        <v>0.52943167776691</v>
       </c>
       <c r="B67" t="n">
-        <v>0.348046749974423</v>
+        <v>0.125020370078958</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>0.138103615215512</v>
+        <v>1.0299276216025</v>
       </c>
       <c r="B68" t="n">
-        <v>0.26041439409998</v>
+        <v>0.175085880867153</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>0.372548834012711</v>
+        <v>0.215482567540043</v>
       </c>
       <c r="B69" t="n">
-        <v>0.341235424717969</v>
+        <v>0.286194963401307</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>0.502636930300055</v>
+        <v>10.0774116146663</v>
       </c>
       <c r="B70" t="n">
-        <v>0.441613581947543</v>
+        <v>0.354762427647084</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>1.15968594409369</v>
+        <v>16.7218789880673</v>
       </c>
       <c r="B71" t="n">
-        <v>0.194276817308661</v>
+        <v>0.425588257074854</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>0.14239620135572</v>
+        <v>0.192425379670852</v>
       </c>
       <c r="B72" t="n">
-        <v>0.0948431767964878</v>
+        <v>0.159272742362585</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>0.136854411296824</v>
+        <v>0.313412183534423</v>
       </c>
       <c r="B73" t="n">
-        <v>0.48107524207312</v>
+        <v>0.254679354583212</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>6.0191782937962</v>
+        <v>59.6285325931928</v>
       </c>
       <c r="B74" t="n">
-        <v>0.332781706222602</v>
+        <v>0.693910037074478</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>12.1427658566582</v>
+        <v>2.40064165265266</v>
       </c>
       <c r="B75" t="n">
-        <v>0.364773041069542</v>
+        <v>0.246833894829698</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>5.65844484523463</v>
+        <v>1.39053121125763</v>
       </c>
       <c r="B76" t="n">
-        <v>0.325308947669354</v>
+        <v>0.417545731675347</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>0.223089911702144</v>
+        <v>2.20299398696063</v>
       </c>
       <c r="B77" t="n">
-        <v>0.263587880831817</v>
+        <v>0.235123953050349</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>3.06203934300229</v>
+        <v>0.901664930234317</v>
       </c>
       <c r="B78" t="n">
-        <v>0.305640313899491</v>
+        <v>0.159850340785969</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>5.58243047887597</v>
+        <v>1.08734913401722</v>
       </c>
       <c r="B79" t="n">
-        <v>0.346122374292061</v>
+        <v>0.190491061055171</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>2.51927106372113</v>
+        <v>0.134957161256193</v>
       </c>
       <c r="B80" t="n">
-        <v>0.261471831540722</v>
+        <v>0.0404373230968683</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>5.62399058769318</v>
+        <v>0.126610928276757</v>
       </c>
       <c r="B81" t="n">
-        <v>0.306326121883852</v>
+        <v>0.141432599721136</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>11.8480635760054</v>
+        <v>3.0598428545951</v>
       </c>
       <c r="B82" t="n">
-        <v>0.37055842103277</v>
+        <v>0.279474396010239</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>0.364628680508359</v>
+        <v>0.314959506061246</v>
       </c>
       <c r="B83" t="n">
-        <v>0.444616418392624</v>
+        <v>0.333727465342314</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>0.185538744003249</v>
+        <v>74.206852323923</v>
       </c>
       <c r="B84" t="n">
-        <v>0.265449616892955</v>
+        <v>0.520196699695764</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>0.332076489050116</v>
+        <v>11.3801843830125</v>
       </c>
       <c r="B85" t="n">
-        <v>0.249863867565152</v>
+        <v>0.53031532547893</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>3.82288742834598</v>
+        <v>0.241516343402116</v>
       </c>
       <c r="B86" t="n">
-        <v>0.309477355585526</v>
+        <v>0.25938448195112</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>2.29550184632256</v>
+        <v>0.355936483983821</v>
       </c>
       <c r="B87" t="n">
-        <v>0.258908498144658</v>
+        <v>0.0891963568957136</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>0.121509289103109</v>
+        <v>0.211253403185129</v>
       </c>
       <c r="B88" t="n">
-        <v>0.314312083237325</v>
+        <v>0.181653801207222</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>0.68597192262838</v>
+        <v>2.41148388281843</v>
       </c>
       <c r="B89" t="n">
-        <v>0.14835000464957</v>
+        <v>0.264299431318147</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>12.0206717967673</v>
+        <v>0.0861066092063539</v>
       </c>
       <c r="B90" t="n">
-        <v>0.38459377039291</v>
+        <v>0.147723760100263</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>0.226085983867484</v>
+        <v>0.515358942563737</v>
       </c>
       <c r="B91" t="n">
-        <v>0.0678524520917668</v>
+        <v>0.126283362891059</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>0.379163679383916</v>
+        <v>4.99441352351654</v>
       </c>
       <c r="B92" t="n">
-        <v>0.119773996384966</v>
+        <v>0.328629720476284</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>1.16605058070267</v>
+        <v>22.0977989523933</v>
       </c>
       <c r="B93" t="n">
-        <v>0.187909649652089</v>
+        <v>0.41246856453562</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>5.74226837430407</v>
+        <v>29.8337337874013</v>
       </c>
       <c r="B94" t="n">
-        <v>0.333847588981508</v>
+        <v>0.453084384892874</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>0.350644749414497</v>
+        <v>9.52446164770418</v>
       </c>
       <c r="B95" t="n">
-        <v>0.288146699137617</v>
+        <v>0.364974846395621</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>0.230479035829919</v>
+        <v>66.1592397248254</v>
       </c>
       <c r="B96" t="n">
-        <v>0.0685081668197375</v>
+        <v>0.532022268085243</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>2.10006998973418</v>
+        <v>0.153748883181095</v>
       </c>
       <c r="B97" t="n">
-        <v>0.228169984796204</v>
+        <v>0.758961818570841</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>2.2793567147637</v>
+        <v>73.4177101651796</v>
       </c>
       <c r="B98" t="n">
-        <v>0.242619458260596</v>
+        <v>0.554856067532398</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>0.870052656481386</v>
+        <v>0.189621579843772</v>
       </c>
       <c r="B99" t="n">
-        <v>0.169590188228875</v>
+        <v>0.451831857161941</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>0.23002639917815</v>
+        <v>0.761758092200652</v>
       </c>
       <c r="B100" t="n">
-        <v>0.232077767327747</v>
+        <v>0.170870444701572</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>1.83476952610217</v>
+        <v>0.354376942734274</v>
       </c>
       <c r="B101" t="n">
-        <v>0.227322673959629</v>
+        <v>0.0958100752210067</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B103" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>7.97940632338061</v>
+        <v>10.7858688664254</v>
       </c>
       <c r="B104" t="n">
-        <v>0.266332204621713</v>
+        <v>0.303713132598372</v>
       </c>
     </row>
   </sheetData>
@@ -3981,18 +3984,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46016.8368950609</v>
+        <v>46026.1351881666</v>
       </c>
       <c r="B2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
